--- a/src/test/resources/ImportTemplate/Recon - Flat File-SQL.xlsx
+++ b/src/test/resources/ImportTemplate/Recon - Flat File-SQL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1694659-764E-43C7-ABFC-D973902635C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E160D303-BCB0-44CA-A9F2-BBD716D19847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,9 +90,6 @@
     <t>targetReadEmptyValueAsNull</t>
   </si>
   <si>
-    <t>R001_FlatFile_SQL--Recon--01</t>
-  </si>
-  <si>
     <t>select * from tblname_1751280108339</t>
   </si>
   <si>
@@ -100,6 +97,9 @@
   </si>
   <si>
     <t>|</t>
+  </si>
+  <si>
+    <t>R00_FlatFile-SQL_Recon</t>
   </si>
 </sst>
 </file>
@@ -517,25 +517,25 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
       </c>
       <c r="L2">
         <v>0</v>

--- a/src/test/resources/ImportTemplate/Recon - Flat File-SQL.xlsx
+++ b/src/test/resources/ImportTemplate/Recon - Flat File-SQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E160D303-BCB0-44CA-A9F2-BBD716D19847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA653E3F-10E3-4B50-AC4E-6F140FCB02FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
     <t>|</t>
   </si>
   <si>
-    <t>R00_FlatFile-SQL_Recon</t>
+    <t>Recon_ImportSQL--File-FlatFile-SQL_Customer</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Recon - Flat File-SQL.xlsx
+++ b/src/test/resources/ImportTemplate/Recon - Flat File-SQL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA653E3F-10E3-4B50-AC4E-6F140FCB02FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68B7180-A8AD-479D-AB44-DB5F79456DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
     <t>|</t>
   </si>
   <si>
-    <t>Recon_ImportSQL--File-FlatFile-SQL_Customer</t>
+    <t>Recon_ImportSQL__File_FlatFile_SQL_Customer</t>
   </si>
 </sst>
 </file>
